--- a/statics/static_sheet.xlsx
+++ b/statics/static_sheet.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UTHIHI\PycharmProjects\MoamProject\PCMail\static_info\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UTHIHI\PycharmProjects\MoamProject\statics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{182F5B07-7079-415C-9196-E138A61C9169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABDABE2-F9F7-42AA-96C1-5B9A10792E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{BEDCD23D-130C-4D40-8649-08CA7512DBD5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{BEDCD23D-130C-4D40-8649-08CA7512DBD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmarks" sheetId="4" r:id="rId1"/>
-    <sheet name="ESG" sheetId="5" r:id="rId2"/>
-    <sheet name="advisers" sheetId="6" r:id="rId3"/>
+    <sheet name="ProductURLs" sheetId="7" r:id="rId2"/>
+    <sheet name="PARP" sheetId="8" r:id="rId3"/>
+    <sheet name="ProspectusURLs" sheetId="9" r:id="rId4"/>
+    <sheet name="ESG" sheetId="5" r:id="rId5"/>
+    <sheet name="advisers" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="Agent">[1]Sheet1!$C$8</definedName>
@@ -48,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="263">
   <si>
     <t>BENCHMARK ID</t>
   </si>
@@ -711,13 +714,139 @@
   </si>
   <si>
     <t>Jan van de ven</t>
+  </si>
+  <si>
+    <t>FULL_NAME</t>
+  </si>
+  <si>
+    <t>ALIAS</t>
+  </si>
+  <si>
+    <t>iShares MSCI Emerging Markets ETF</t>
+  </si>
+  <si>
+    <t>Eurozone</t>
+  </si>
+  <si>
+    <t>VS</t>
+  </si>
+  <si>
+    <t>US Technology</t>
+  </si>
+  <si>
+    <t>Eurozone Banks</t>
+  </si>
+  <si>
+    <t>Eurozone Dividend</t>
+  </si>
+  <si>
+    <t>JPN</t>
+  </si>
+  <si>
+    <t>EM</t>
+  </si>
+  <si>
+    <t>Global Dividend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRODUCT_TYPE </t>
+  </si>
+  <si>
+    <t>BROCHURE_LABEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BROCHURE_URL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIDEO_URL  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIDEO_LABEL_MARKETING </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIDEO_LABEL_PC   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger Plus Note </t>
+  </si>
+  <si>
+    <t>Memory Coupon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Index Garantie Note </t>
+  </si>
+  <si>
+    <t>Index Garantie Note Capped</t>
+  </si>
+  <si>
+    <t>Fixed Rate Note</t>
+  </si>
+  <si>
+    <t>General Brochure Trigger Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Brochure Memory Coupon </t>
+  </si>
+  <si>
+    <t>General Brochure Index Garantie Notes</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/765679154</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/765678480</t>
+  </si>
+  <si>
+    <t>Hoe werkt een Garantie note?</t>
+  </si>
+  <si>
+    <t>Hoe werkt een Trigger note?</t>
+  </si>
+  <si>
+    <t>Trigger Notes – Product Video</t>
+  </si>
+  <si>
+    <t>Index Garantie Notes – Product Video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARP_DATE </t>
+  </si>
+  <si>
+    <t>CODE</t>
+  </si>
+  <si>
+    <t>LABEL</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>DIP</t>
+  </si>
+  <si>
+    <t>SNIP</t>
+  </si>
+  <si>
+    <t>https://markets.vanlanschotkempen.com/file/GetFile/uploadedfiles/Documents/FvL%2025328%20BRO%20SP%20Trigger%20Notes.pdf</t>
+  </si>
+  <si>
+    <t>https://markets.vanlanschotkempen.com/file/GetFile/uploadedfiles/Documents/FvL%2025329%20BRO%20Memory%20Coupon%20Notes.pdf</t>
+  </si>
+  <si>
+    <t>https://markets.vanlanschotkempen.com/file/GetFile/uploadedfiles/Documents/FvL%2025326%20BRO%20Index%20Garantie%20Notes.pdf</t>
+  </si>
+  <si>
+    <t>https://www.vanlanschotkempen.com/-/media/files/documents/corporate/investor-relations-en/debt-investors/library/snip/2025/prospectus/securities-note---30-may-2025.ashx</t>
+  </si>
+  <si>
+    <t>https://www.vanlanschotkempen.com/-/media/files/documents/corporate/investor-relations-en/debt-investors/library/dip/2025/prospectus/securities-note---15-may-2025.ashx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -760,6 +889,14 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -824,10 +961,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -847,8 +985,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1203,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69353C34-D752-4EE8-9624-BFD9BF9C419E}">
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -1211,7 +1356,7 @@
     <col min="3" max="3" width="53.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1221,8 +1366,14 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1233,7 +1384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1244,7 +1395,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1255,7 +1406,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1266,7 +1417,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1275,7 +1426,7 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1286,7 +1437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1296,8 +1447,11 @@
       <c r="C8" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E8" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1307,8 +1461,11 @@
       <c r="C9" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
@@ -1318,8 +1475,11 @@
       <c r="C10" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E10" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -1330,7 +1490,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>30</v>
       </c>
@@ -1339,7 +1499,7 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>32</v>
       </c>
@@ -1348,7 +1508,7 @@
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
@@ -1359,7 +1519,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -1368,7 +1528,7 @@
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -1535,7 +1695,7 @@
       </c>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>78</v>
       </c>
@@ -1546,7 +1706,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>81</v>
       </c>
@@ -1557,7 +1717,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>84</v>
       </c>
@@ -1566,7 +1726,7 @@
       </c>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>86</v>
       </c>
@@ -1575,7 +1735,7 @@
       </c>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>88</v>
       </c>
@@ -1586,7 +1746,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>91</v>
       </c>
@@ -1595,7 +1755,7 @@
       </c>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>93</v>
       </c>
@@ -1604,7 +1764,7 @@
       </c>
       <c r="C39" s="1"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>95</v>
       </c>
@@ -1614,8 +1774,11 @@
       <c r="C40" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>98</v>
       </c>
@@ -1625,8 +1788,11 @@
       <c r="C41" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E41" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>101</v>
       </c>
@@ -1637,7 +1803,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>104</v>
       </c>
@@ -1648,7 +1814,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>107</v>
       </c>
@@ -1659,7 +1825,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>110</v>
       </c>
@@ -1669,8 +1835,11 @@
       <c r="C45" s="1" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E45" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>113</v>
       </c>
@@ -1679,7 +1848,7 @@
       </c>
       <c r="C46" s="1"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>115</v>
       </c>
@@ -1689,8 +1858,11 @@
       <c r="C47" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E47" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>117</v>
       </c>
@@ -1701,7 +1873,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>120</v>
       </c>
@@ -1712,7 +1884,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>123</v>
       </c>
@@ -1723,7 +1895,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>126</v>
       </c>
@@ -1734,7 +1906,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>129</v>
       </c>
@@ -1745,7 +1917,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>132</v>
       </c>
@@ -1755,8 +1927,11 @@
       <c r="C53" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>135</v>
       </c>
@@ -1767,7 +1942,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>138</v>
       </c>
@@ -1776,7 +1951,7 @@
       </c>
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -1787,7 +1962,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>66</v>
       </c>
@@ -1796,9 +1971,15 @@
       </c>
       <c r="C57" s="1"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>0</v>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D58" t="s">
+        <v>223</v>
+      </c>
+      <c r="E58" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -1808,6 +1989,243 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56C607-A183-435E-A0D0-24867AE7F84C}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="E2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="E4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="E5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{ABEECBC3-DF88-4F86-9413-AB43BA5FB220}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{FD8FCD8E-689E-4853-8179-6ABFB2E864B6}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{872BE184-7ED4-4EC4-800C-D78C562180CE}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{32EAF4EF-6B95-49A1-8A3B-CA739937335A}"/>
+    <hyperlink ref="C4" r:id="rId5" xr:uid="{49AA75E1-08D0-45BC-8A20-5D65E0032086}"/>
+    <hyperlink ref="C5" r:id="rId6" xr:uid="{6191C3CC-9688-48B9-8917-D9A18A4A07CB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0761BC0-49B6-42C4-BEB7-B3482B0EF469}">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" s="16">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" s="16">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="16">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="16">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="16">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G17" s="17"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73945FBB-4873-4441-9667-D3AAACEC290F}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>261</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{FFF2D0F5-473B-4FC1-92A2-A0D53444A195}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{8E173CD5-2F21-457F-A09C-EC6471120376}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD660241-4EC6-4BC1-A445-D102A6866814}">
   <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2121,7 +2539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C35522-9FC3-4717-8750-CF62E6EB6BC3}">
   <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/statics/static_sheet.xlsx
+++ b/statics/static_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UTHIHI\PycharmProjects\MoamProject\statics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABDABE2-F9F7-42AA-96C1-5B9A10792E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B415B3D-02D8-4E1B-832C-F7E0DFC8A124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{BEDCD23D-130C-4D40-8649-08CA7512DBD5}"/>
+    <workbookView xWindow="28680" yWindow="1620" windowWidth="29040" windowHeight="17520" xr2:uid="{BEDCD23D-130C-4D40-8649-08CA7512DBD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmarks" sheetId="4" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="266">
   <si>
     <t>BENCHMARK ID</t>
   </si>
@@ -840,6 +840,15 @@
   </si>
   <si>
     <t>https://www.vanlanschotkempen.com/-/media/files/documents/corporate/investor-relations-en/debt-investors/library/dip/2025/prospectus/securities-note---15-may-2025.ashx</t>
+  </si>
+  <si>
+    <t>IGV US</t>
+  </si>
+  <si>
+    <t>iShares Expanded Tech-Software Sector ETF</t>
+  </si>
+  <si>
+    <t>US Software</t>
   </si>
 </sst>
 </file>
@@ -965,7 +974,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -991,6 +1000,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1348,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69353C34-D752-4EE8-9624-BFD9BF9C419E}">
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -1980,6 +1991,17 @@
       </c>
       <c r="E58" t="s">
         <v>230</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D59" t="s">
+        <v>264</v>
+      </c>
+      <c r="E59" t="s">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -2227,7 +2249,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD660241-4EC6-4BC1-A445-D102A6866814}">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -2531,6 +2553,14 @@
         <v>21</v>
       </c>
       <c r="B38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="B39" s="20">
         <v>3</v>
       </c>
     </row>
